--- a/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3be574a0596446d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfc2f753599bb4480"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfc2f753599bb4480"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb6ea624ff232432d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb6ea624ff232432d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R302c92eaf1a74ebb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R302c92eaf1a74ebb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcf573735144246aa"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcf573735144246aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R529e53c6f236459b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R529e53c6f236459b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R615827435db749d8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R615827435db749d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R065d8ec86e404cef"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R065d8ec86e404cef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6d2fe24727a84752"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6d2fe24727a84752"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3cb18b56c7df46d6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3cb18b56c7df46d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6c28c11f5e5149db"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6c28c11f5e5149db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra17ab6c6323a4d88"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra17ab6c6323a4d88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb5b5ca4d0bce4859"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb5b5ca4d0bce4859"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcbd28aee277c4e27"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcbd28aee277c4e27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdc53d82207944376"/>
   </x:sheets>
 </x:workbook>
 </file>
